--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,6 +2227,1278 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126017267</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92504</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>834367</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7449195</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126017263</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92510</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>834167</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7449043</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126017268</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92502</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>834372</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7449188</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126017265</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92535</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>834362</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7449190</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126017273</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92502</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>834231</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7449250</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126017266</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92546</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>834366</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7449190</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126017270</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92526</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>834235</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7449241</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126017274</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92502</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>834090</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7449361</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126017264</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92502</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>834158</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7449042</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126017269</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92522</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>834373</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7449196</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126017272</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92526</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>834286</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7449184</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126017262</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92504</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Narken, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>833987</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7449169</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>126017267</v>
       </c>
       <c r="B16" t="n">
-        <v>92504</v>
+        <v>92512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>126017263</v>
       </c>
       <c r="B17" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>126017268</v>
       </c>
       <c r="B18" t="n">
-        <v>92502</v>
+        <v>92510</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>126017265</v>
       </c>
       <c r="B19" t="n">
-        <v>92535</v>
+        <v>92543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>126017273</v>
       </c>
       <c r="B20" t="n">
-        <v>92502</v>
+        <v>92510</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>126017266</v>
       </c>
       <c r="B21" t="n">
-        <v>92546</v>
+        <v>92554</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>126017270</v>
       </c>
       <c r="B22" t="n">
-        <v>92526</v>
+        <v>92534</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>126017274</v>
       </c>
       <c r="B23" t="n">
-        <v>92502</v>
+        <v>92510</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>126017264</v>
       </c>
       <c r="B24" t="n">
-        <v>92502</v>
+        <v>92510</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>126017269</v>
       </c>
       <c r="B25" t="n">
-        <v>92522</v>
+        <v>92530</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>126017272</v>
       </c>
       <c r="B26" t="n">
-        <v>92526</v>
+        <v>92534</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>126017262</v>
       </c>
       <c r="B27" t="n">
-        <v>92504</v>
+        <v>92512</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>126017267</v>
       </c>
       <c r="B16" t="n">
-        <v>92512</v>
+        <v>92516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>126017263</v>
       </c>
       <c r="B17" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>126017268</v>
       </c>
       <c r="B18" t="n">
-        <v>92510</v>
+        <v>92514</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>126017265</v>
       </c>
       <c r="B19" t="n">
-        <v>92543</v>
+        <v>92547</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>126017273</v>
       </c>
       <c r="B20" t="n">
-        <v>92510</v>
+        <v>92514</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>126017266</v>
       </c>
       <c r="B21" t="n">
-        <v>92554</v>
+        <v>92558</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>126017270</v>
       </c>
       <c r="B22" t="n">
-        <v>92534</v>
+        <v>92538</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>126017274</v>
       </c>
       <c r="B23" t="n">
-        <v>92510</v>
+        <v>92514</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>126017264</v>
       </c>
       <c r="B24" t="n">
-        <v>92510</v>
+        <v>92514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>126017269</v>
       </c>
       <c r="B25" t="n">
-        <v>92530</v>
+        <v>92534</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>126017272</v>
       </c>
       <c r="B26" t="n">
-        <v>92534</v>
+        <v>92538</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>126017262</v>
       </c>
       <c r="B27" t="n">
-        <v>92512</v>
+        <v>92516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2759,10 +2759,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126017266</v>
+        <v>126017270</v>
       </c>
       <c r="B21" t="n">
-        <v>92558</v>
+        <v>92538</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,21 +2770,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>834366</v>
+        <v>834235</v>
       </c>
       <c r="R21" t="n">
-        <v>7449190</v>
+        <v>7449241</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126017270</v>
+        <v>126017266</v>
       </c>
       <c r="B22" t="n">
-        <v>92538</v>
+        <v>92558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834235</v>
+        <v>834366</v>
       </c>
       <c r="R22" t="n">
-        <v>7449241</v>
+        <v>7449190</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -3077,32 +3077,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126017264</v>
+        <v>126017269</v>
       </c>
       <c r="B24" t="n">
-        <v>92514</v>
+        <v>92534</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>834158</v>
+        <v>834373</v>
       </c>
       <c r="R24" t="n">
-        <v>7449042</v>
+        <v>7449196</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3183,32 +3183,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126017269</v>
+        <v>126017264</v>
       </c>
       <c r="B25" t="n">
-        <v>92534</v>
+        <v>92514</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>834373</v>
+        <v>834158</v>
       </c>
       <c r="R25" t="n">
-        <v>7449196</v>
+        <v>7449042</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -3077,32 +3077,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126017269</v>
+        <v>126017264</v>
       </c>
       <c r="B24" t="n">
-        <v>92534</v>
+        <v>92514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>834373</v>
+        <v>834158</v>
       </c>
       <c r="R24" t="n">
-        <v>7449196</v>
+        <v>7449042</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3183,32 +3183,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126017264</v>
+        <v>126017269</v>
       </c>
       <c r="B25" t="n">
-        <v>92514</v>
+        <v>92534</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>834158</v>
+        <v>834373</v>
       </c>
       <c r="R25" t="n">
-        <v>7449042</v>
+        <v>7449196</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>126017267</v>
       </c>
       <c r="B16" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>126017263</v>
       </c>
       <c r="B17" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>126017268</v>
       </c>
       <c r="B18" t="n">
-        <v>92514</v>
+        <v>92516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>126017265</v>
       </c>
       <c r="B19" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>126017273</v>
       </c>
       <c r="B20" t="n">
-        <v>92514</v>
+        <v>92516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126017270</v>
+        <v>126017266</v>
       </c>
       <c r="B21" t="n">
-        <v>92538</v>
+        <v>92560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,21 +2770,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>834235</v>
+        <v>834366</v>
       </c>
       <c r="R21" t="n">
-        <v>7449241</v>
+        <v>7449190</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126017266</v>
+        <v>126017270</v>
       </c>
       <c r="B22" t="n">
-        <v>92558</v>
+        <v>92540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834366</v>
+        <v>834235</v>
       </c>
       <c r="R22" t="n">
-        <v>7449190</v>
+        <v>7449241</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2974,7 +2974,7 @@
         <v>126017274</v>
       </c>
       <c r="B23" t="n">
-        <v>92514</v>
+        <v>92516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>126017264</v>
       </c>
       <c r="B24" t="n">
-        <v>92514</v>
+        <v>92516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>126017269</v>
       </c>
       <c r="B25" t="n">
-        <v>92534</v>
+        <v>92536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>126017272</v>
       </c>
       <c r="B26" t="n">
-        <v>92538</v>
+        <v>92540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>126017262</v>
       </c>
       <c r="B27" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2759,10 +2759,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126017266</v>
+        <v>126017270</v>
       </c>
       <c r="B21" t="n">
-        <v>92560</v>
+        <v>92540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,21 +2770,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>834366</v>
+        <v>834235</v>
       </c>
       <c r="R21" t="n">
-        <v>7449190</v>
+        <v>7449241</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126017270</v>
+        <v>126017266</v>
       </c>
       <c r="B22" t="n">
-        <v>92540</v>
+        <v>92560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834235</v>
+        <v>834366</v>
       </c>
       <c r="R22" t="n">
-        <v>7449241</v>
+        <v>7449190</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>126017267</v>
       </c>
       <c r="B16" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>126017263</v>
       </c>
       <c r="B17" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>126017268</v>
       </c>
       <c r="B18" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>126017265</v>
       </c>
       <c r="B19" t="n">
-        <v>92549</v>
+        <v>92551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>126017273</v>
       </c>
       <c r="B20" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>126017270</v>
       </c>
       <c r="B21" t="n">
-        <v>92540</v>
+        <v>92542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>126017266</v>
       </c>
       <c r="B22" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>126017274</v>
       </c>
       <c r="B23" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>126017264</v>
       </c>
       <c r="B24" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>126017269</v>
       </c>
       <c r="B25" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>126017272</v>
       </c>
       <c r="B26" t="n">
-        <v>92540</v>
+        <v>92542</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>126017262</v>
       </c>
       <c r="B27" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>126017267</v>
       </c>
       <c r="B16" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126017263</v>
+        <v>126017268</v>
       </c>
       <c r="B17" t="n">
-        <v>92526</v>
+        <v>92520</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>834167</v>
+        <v>834372</v>
       </c>
       <c r="R17" t="n">
-        <v>7449043</v>
+        <v>7449188</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2441,32 +2441,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126017268</v>
+        <v>126017263</v>
       </c>
       <c r="B18" t="n">
-        <v>92518</v>
+        <v>92528</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>834372</v>
+        <v>834167</v>
       </c>
       <c r="R18" t="n">
-        <v>7449188</v>
+        <v>7449043</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2550,7 +2550,7 @@
         <v>126017265</v>
       </c>
       <c r="B19" t="n">
-        <v>92551</v>
+        <v>92553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>126017273</v>
       </c>
       <c r="B20" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>126017270</v>
       </c>
       <c r="B21" t="n">
-        <v>92542</v>
+        <v>92544</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>126017266</v>
       </c>
       <c r="B22" t="n">
-        <v>92562</v>
+        <v>92564</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>126017274</v>
       </c>
       <c r="B23" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>126017264</v>
       </c>
       <c r="B24" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>126017269</v>
       </c>
       <c r="B25" t="n">
-        <v>92538</v>
+        <v>92540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>126017272</v>
       </c>
       <c r="B26" t="n">
-        <v>92542</v>
+        <v>92544</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>126017262</v>
       </c>
       <c r="B27" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>126017267</v>
       </c>
       <c r="B16" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126017268</v>
+        <v>126017263</v>
       </c>
       <c r="B17" t="n">
-        <v>92520</v>
+        <v>92532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>834372</v>
+        <v>834167</v>
       </c>
       <c r="R17" t="n">
-        <v>7449188</v>
+        <v>7449043</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2441,32 +2441,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126017263</v>
+        <v>126017268</v>
       </c>
       <c r="B18" t="n">
-        <v>92528</v>
+        <v>92524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>834167</v>
+        <v>834372</v>
       </c>
       <c r="R18" t="n">
-        <v>7449043</v>
+        <v>7449188</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2550,7 +2550,7 @@
         <v>126017265</v>
       </c>
       <c r="B19" t="n">
-        <v>92553</v>
+        <v>92557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>126017273</v>
       </c>
       <c r="B20" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126017270</v>
+        <v>126017266</v>
       </c>
       <c r="B21" t="n">
-        <v>92544</v>
+        <v>92568</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,21 +2770,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>834235</v>
+        <v>834366</v>
       </c>
       <c r="R21" t="n">
-        <v>7449241</v>
+        <v>7449190</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126017266</v>
+        <v>126017270</v>
       </c>
       <c r="B22" t="n">
-        <v>92564</v>
+        <v>92548</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834366</v>
+        <v>834235</v>
       </c>
       <c r="R22" t="n">
-        <v>7449190</v>
+        <v>7449241</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2974,7 +2974,7 @@
         <v>126017274</v>
       </c>
       <c r="B23" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>126017264</v>
       </c>
       <c r="B24" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>126017269</v>
       </c>
       <c r="B25" t="n">
-        <v>92540</v>
+        <v>92544</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>126017272</v>
       </c>
       <c r="B26" t="n">
-        <v>92544</v>
+        <v>92548</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>126017262</v>
       </c>
       <c r="B27" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2547,10 +2547,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126017265</v>
+        <v>126017273</v>
       </c>
       <c r="B19" t="n">
-        <v>92557</v>
+        <v>92524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,21 +2558,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>834362</v>
+        <v>834231</v>
       </c>
       <c r="R19" t="n">
-        <v>7449190</v>
+        <v>7449250</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126017273</v>
+        <v>126017265</v>
       </c>
       <c r="B20" t="n">
-        <v>92524</v>
+        <v>92557</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2664,21 +2664,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>834231</v>
+        <v>834362</v>
       </c>
       <c r="R20" t="n">
-        <v>7449250</v>
+        <v>7449190</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126017264</v>
+        <v>126017269</v>
       </c>
       <c r="B24" t="n">
-        <v>92524</v>
+        <v>92544</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>834158</v>
+        <v>834373</v>
       </c>
       <c r="R24" t="n">
-        <v>7449042</v>
+        <v>7449196</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3183,32 +3183,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126017269</v>
+        <v>126017264</v>
       </c>
       <c r="B25" t="n">
-        <v>92544</v>
+        <v>92524</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>834373</v>
+        <v>834158</v>
       </c>
       <c r="R25" t="n">
-        <v>7449196</v>
+        <v>7449042</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2335,32 +2335,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126017263</v>
+        <v>126017268</v>
       </c>
       <c r="B17" t="n">
-        <v>92532</v>
+        <v>92524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>834167</v>
+        <v>834372</v>
       </c>
       <c r="R17" t="n">
-        <v>7449043</v>
+        <v>7449188</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2441,32 +2441,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126017268</v>
+        <v>126017263</v>
       </c>
       <c r="B18" t="n">
-        <v>92524</v>
+        <v>92532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>834372</v>
+        <v>834167</v>
       </c>
       <c r="R18" t="n">
-        <v>7449188</v>
+        <v>7449043</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126017266</v>
+        <v>126017270</v>
       </c>
       <c r="B21" t="n">
-        <v>92568</v>
+        <v>92548</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,21 +2770,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>834366</v>
+        <v>834235</v>
       </c>
       <c r="R21" t="n">
-        <v>7449190</v>
+        <v>7449241</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126017270</v>
+        <v>126017266</v>
       </c>
       <c r="B22" t="n">
-        <v>92548</v>
+        <v>92568</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834235</v>
+        <v>834366</v>
       </c>
       <c r="R22" t="n">
-        <v>7449241</v>
+        <v>7449190</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2759,10 +2759,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126017270</v>
+        <v>126017266</v>
       </c>
       <c r="B21" t="n">
-        <v>92548</v>
+        <v>92568</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,21 +2770,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>834235</v>
+        <v>834366</v>
       </c>
       <c r="R21" t="n">
-        <v>7449241</v>
+        <v>7449190</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126017266</v>
+        <v>126017270</v>
       </c>
       <c r="B22" t="n">
-        <v>92568</v>
+        <v>92548</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834366</v>
+        <v>834235</v>
       </c>
       <c r="R22" t="n">
-        <v>7449190</v>
+        <v>7449241</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2335,32 +2335,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126017268</v>
+        <v>126017263</v>
       </c>
       <c r="B17" t="n">
-        <v>92524</v>
+        <v>92532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>834372</v>
+        <v>834167</v>
       </c>
       <c r="R17" t="n">
-        <v>7449188</v>
+        <v>7449043</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2441,32 +2441,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126017263</v>
+        <v>126017268</v>
       </c>
       <c r="B18" t="n">
-        <v>92532</v>
+        <v>92524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>834167</v>
+        <v>834372</v>
       </c>
       <c r="R18" t="n">
-        <v>7449043</v>
+        <v>7449188</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126017273</v>
+        <v>126017265</v>
       </c>
       <c r="B19" t="n">
-        <v>92524</v>
+        <v>92557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,21 +2558,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>834231</v>
+        <v>834362</v>
       </c>
       <c r="R19" t="n">
-        <v>7449250</v>
+        <v>7449190</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126017265</v>
+        <v>126017273</v>
       </c>
       <c r="B20" t="n">
-        <v>92557</v>
+        <v>92524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2664,21 +2664,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>834362</v>
+        <v>834231</v>
       </c>
       <c r="R20" t="n">
-        <v>7449190</v>
+        <v>7449250</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126017269</v>
+        <v>126017264</v>
       </c>
       <c r="B24" t="n">
-        <v>92544</v>
+        <v>92524</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>834373</v>
+        <v>834158</v>
       </c>
       <c r="R24" t="n">
-        <v>7449196</v>
+        <v>7449042</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3183,32 +3183,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126017264</v>
+        <v>126017269</v>
       </c>
       <c r="B25" t="n">
-        <v>92524</v>
+        <v>92544</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>834158</v>
+        <v>834373</v>
       </c>
       <c r="R25" t="n">
-        <v>7449042</v>
+        <v>7449196</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2232,7 +2232,7 @@
         <v>126017267</v>
       </c>
       <c r="B16" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>126017263</v>
       </c>
       <c r="B17" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>126017268</v>
       </c>
       <c r="B18" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>126017265</v>
       </c>
       <c r="B19" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>126017273</v>
       </c>
       <c r="B20" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126017266</v>
+        <v>126017270</v>
       </c>
       <c r="B21" t="n">
-        <v>92568</v>
+        <v>92551</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,21 +2770,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>834366</v>
+        <v>834235</v>
       </c>
       <c r="R21" t="n">
-        <v>7449190</v>
+        <v>7449241</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126017270</v>
+        <v>126017266</v>
       </c>
       <c r="B22" t="n">
-        <v>92548</v>
+        <v>92571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834235</v>
+        <v>834366</v>
       </c>
       <c r="R22" t="n">
-        <v>7449241</v>
+        <v>7449190</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2974,7 +2974,7 @@
         <v>126017274</v>
       </c>
       <c r="B23" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>126017264</v>
       </c>
       <c r="B24" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>126017269</v>
       </c>
       <c r="B25" t="n">
-        <v>92544</v>
+        <v>92547</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>126017272</v>
       </c>
       <c r="B26" t="n">
-        <v>92548</v>
+        <v>92551</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>126017262</v>
       </c>
       <c r="B27" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2759,10 +2759,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126017270</v>
+        <v>126017266</v>
       </c>
       <c r="B21" t="n">
-        <v>92551</v>
+        <v>92571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,21 +2770,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>834235</v>
+        <v>834366</v>
       </c>
       <c r="R21" t="n">
-        <v>7449241</v>
+        <v>7449190</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126017266</v>
+        <v>126017270</v>
       </c>
       <c r="B22" t="n">
-        <v>92571</v>
+        <v>92551</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834366</v>
+        <v>834235</v>
       </c>
       <c r="R22" t="n">
-        <v>7449190</v>
+        <v>7449241</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -2759,10 +2759,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126017266</v>
+        <v>126017270</v>
       </c>
       <c r="B21" t="n">
-        <v>92571</v>
+        <v>92551</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,21 +2770,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>834366</v>
+        <v>834235</v>
       </c>
       <c r="R21" t="n">
-        <v>7449190</v>
+        <v>7449241</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126017270</v>
+        <v>126017266</v>
       </c>
       <c r="B22" t="n">
-        <v>92551</v>
+        <v>92571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>834235</v>
+        <v>834366</v>
       </c>
       <c r="R22" t="n">
-        <v>7449241</v>
+        <v>7449190</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126017264</v>
+        <v>126017269</v>
       </c>
       <c r="B24" t="n">
-        <v>92527</v>
+        <v>92547</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>834158</v>
+        <v>834373</v>
       </c>
       <c r="R24" t="n">
-        <v>7449042</v>
+        <v>7449196</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3183,32 +3183,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126017269</v>
+        <v>126017264</v>
       </c>
       <c r="B25" t="n">
-        <v>92547</v>
+        <v>92527</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>834373</v>
+        <v>834158</v>
       </c>
       <c r="R25" t="n">
-        <v>7449196</v>
+        <v>7449042</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -3077,32 +3077,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126017269</v>
+        <v>126017264</v>
       </c>
       <c r="B24" t="n">
-        <v>92547</v>
+        <v>92527</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>834373</v>
+        <v>834158</v>
       </c>
       <c r="R24" t="n">
-        <v>7449196</v>
+        <v>7449042</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3183,32 +3183,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126017264</v>
+        <v>126017269</v>
       </c>
       <c r="B25" t="n">
-        <v>92527</v>
+        <v>92547</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>834158</v>
+        <v>834373</v>
       </c>
       <c r="R25" t="n">
-        <v>7449042</v>
+        <v>7449196</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 4703-2025 artfynd.xlsx
+++ b/artfynd/A 4703-2025 artfynd.xlsx
@@ -3077,32 +3077,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126017264</v>
+        <v>126017269</v>
       </c>
       <c r="B24" t="n">
-        <v>92527</v>
+        <v>92547</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>834158</v>
+        <v>834373</v>
       </c>
       <c r="R24" t="n">
-        <v>7449042</v>
+        <v>7449196</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3183,32 +3183,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126017269</v>
+        <v>126017264</v>
       </c>
       <c r="B25" t="n">
-        <v>92547</v>
+        <v>92527</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>834373</v>
+        <v>834158</v>
       </c>
       <c r="R25" t="n">
-        <v>7449196</v>
+        <v>7449042</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
